--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46274</v>
+        <v>46302</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3633,21 +3633,21 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46300</v>
+        <v>46318</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3693,11 +3693,11 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46323</v>
+        <v>46342</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4713,16 +4713,16 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
@@ -4743,16 +4743,16 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3273,37 +3273,37 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>4º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46288</v>
+        <v>46316</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
@@ -3372,37 +3372,37 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46323</v>
+        <v>46259</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46259</v>
+        <v>46329</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -3444,25 +3444,25 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46329</v>
+        <v>46265</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3504,16 +3504,16 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3543,21 +3543,21 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46274</v>
+        <v>46302</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46302</v>
+        <v>46318</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3633,21 +3633,21 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3663,11 +3663,11 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46323</v>
+        <v>46342</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3677,14 +3677,14 @@
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46342</v>
+        <v>46276</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46276</v>
+        <v>46304</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
@@ -3744,30 +3744,30 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46304</v>
+        <v>46268</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46276</v>
+        <v>46304</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3903,11 +3903,11 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46314</v>
+        <v>46331</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3917,23 +3917,23 @@
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46331</v>
+        <v>46268</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3959,11 +3959,11 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46268</v>
+        <v>46282</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46282</v>
+        <v>46331</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4019,45 +4019,45 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46331</v>
+        <v>46342</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46342</v>
+        <v>46274</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4083,21 +4083,21 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -4109,15 +4109,15 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4139,11 +4139,11 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46281</v>
+        <v>46323</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
@@ -4169,11 +4169,11 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46323</v>
+        <v>46337</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
@@ -4199,55 +4199,55 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46338</v>
+        <v>46265</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4379,11 +4379,11 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46281</v>
+        <v>46316</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
@@ -4422,12 +4422,12 @@
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4439,11 +4439,11 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4499,11 +4499,11 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46330</v>
+        <v>46337</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
@@ -4512,42 +4512,42 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46337</v>
+        <v>46282</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46282</v>
+        <v>46317</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46317</v>
+        <v>46331</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
@@ -4602,37 +4602,37 @@
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46331</v>
+        <v>46269</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>46269</v>
+        <v>46304</v>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
@@ -4674,30 +4674,30 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>46304</v>
+        <v>46267</v>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>46267</v>
+        <v>46316</v>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
@@ -4734,30 +4734,30 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>46316</v>
+        <v>46266</v>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>46266</v>
+        <v>46315</v>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
@@ -4794,16 +4794,16 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>46315</v>
+        <v>46273</v>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>11º e 12º tempos</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>46273</v>
+        <v>46315</v>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -4851,38 +4851,8 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C147" s="5" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="F147" s="6" t="inlineStr">
-        <is>
-          <t>12C1, 12C2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:F147"/>
+  <autoFilter ref="A2:F146"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2964,20 +2964,20 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46300</v>
+        <v>46275</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3003,21 +3003,21 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46286</v>
+        <v>46336</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3063,37 +3063,37 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46336</v>
+        <v>46344</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46344</v>
+        <v>46267</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46267</v>
+        <v>46316</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
@@ -3144,20 +3144,20 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46316</v>
+        <v>46259</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46259</v>
+        <v>46315</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3204,30 +3204,30 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46315</v>
+        <v>46297</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3243,37 +3243,37 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46297</v>
+        <v>46323</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46288</v>
+        <v>46316</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,37 +3342,37 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46323</v>
+        <v>46259</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46259</v>
+        <v>46329</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -3414,25 +3414,25 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46329</v>
+        <v>46265</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
@@ -3474,16 +3474,16 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46274</v>
+        <v>46302</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46302</v>
+        <v>46318</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3633,11 +3633,11 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46323</v>
+        <v>46342</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
@@ -3647,14 +3647,14 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46342</v>
+        <v>46276</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46276</v>
+        <v>46304</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
@@ -3714,30 +3714,30 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46304</v>
+        <v>46268</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46276</v>
+        <v>46304</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3843,67 +3843,67 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46314</v>
+        <v>46268</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46331</v>
+        <v>46282</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46268</v>
+        <v>46331</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46282</v>
+        <v>46342</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
@@ -3984,25 +3984,25 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46331</v>
+        <v>46274</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4014,25 +4014,25 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46342</v>
+        <v>46280</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -4049,11 +4049,11 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -4083,21 +4083,21 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46280</v>
+        <v>46323</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46281</v>
+        <v>46337</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
@@ -4143,106 +4143,106 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46323</v>
+        <v>46338</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46337</v>
+        <v>46265</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46338</v>
+        <v>46321</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
@@ -4254,25 +4254,25 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46321</v>
+        <v>46274</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4302,12 +4302,12 @@
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4349,11 +4349,11 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46274</v>
+        <v>46316</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4379,11 +4379,11 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46281</v>
+        <v>46323</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -4409,11 +4409,11 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46316</v>
+        <v>46330</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
@@ -4439,11 +4439,11 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46323</v>
+        <v>46337</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -4464,25 +4464,25 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46330</v>
+        <v>46282</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -4494,30 +4494,30 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46337</v>
+        <v>46317</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46282</v>
+        <v>46331</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
@@ -4542,67 +4542,67 @@
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46317</v>
+        <v>46269</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46331</v>
+        <v>46304</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
@@ -4614,136 +4614,136 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
@@ -4752,24 +4752,24 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>11º e 12º tempos</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C144" s="9" t="n">
@@ -4782,77 +4782,17 @@
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="n">
-        <v>46273</v>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C146" s="9" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D146" s="10" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E146" s="10" t="inlineStr">
-        <is>
-          <t>10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="F146" s="10" t="inlineStr">
-        <is>
-          <t>12C1, 12C2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:F146"/>
+  <autoFilter ref="A2:F144"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -2952,7 +2952,7 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -2964,20 +2964,20 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46300</v>
+        <v>46275</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3003,21 +3003,21 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46286</v>
+        <v>46336</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3063,37 +3063,37 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46336</v>
+        <v>46344</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46344</v>
+        <v>46267</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46267</v>
+        <v>46316</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
@@ -3144,20 +3144,20 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46316</v>
+        <v>46259</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46259</v>
+        <v>46315</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3204,30 +3204,30 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46315</v>
+        <v>46297</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3243,37 +3243,37 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46297</v>
+        <v>46323</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46288</v>
+        <v>46316</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,37 +3342,37 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46323</v>
+        <v>46259</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46259</v>
+        <v>46329</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -3414,25 +3414,25 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46329</v>
+        <v>46265</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
@@ -3474,16 +3474,16 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46274</v>
+        <v>46302</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46302</v>
+        <v>46318</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3633,11 +3633,11 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46323</v>
+        <v>46342</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
@@ -3647,14 +3647,14 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46342</v>
+        <v>46276</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46276</v>
+        <v>46304</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
@@ -3714,30 +3714,30 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46304</v>
+        <v>46268</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46276</v>
+        <v>46304</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3843,67 +3843,67 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46314</v>
+        <v>46268</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46331</v>
+        <v>46282</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46268</v>
+        <v>46331</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46282</v>
+        <v>46342</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
@@ -3984,25 +3984,25 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46331</v>
+        <v>46274</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4014,25 +4014,25 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46342</v>
+        <v>46280</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -4049,11 +4049,11 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -4083,21 +4083,21 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46280</v>
+        <v>46323</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46281</v>
+        <v>46337</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
@@ -4143,106 +4143,106 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46323</v>
+        <v>46338</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46337</v>
+        <v>46265</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46338</v>
+        <v>46321</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
@@ -4254,25 +4254,25 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46321</v>
+        <v>46274</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4302,12 +4302,12 @@
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4349,11 +4349,11 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46274</v>
+        <v>46316</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4379,11 +4379,11 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46281</v>
+        <v>46323</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -4409,11 +4409,11 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46316</v>
+        <v>46330</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
@@ -4439,11 +4439,11 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46323</v>
+        <v>46337</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -4464,25 +4464,25 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46330</v>
+        <v>46282</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -4494,30 +4494,30 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46337</v>
+        <v>46317</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46282</v>
+        <v>46331</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
@@ -4542,67 +4542,67 @@
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46317</v>
+        <v>46269</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46331</v>
+        <v>46304</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
@@ -4614,136 +4614,136 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
@@ -4752,24 +4752,24 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>11º e 12º tempos</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C144" s="9" t="n">
@@ -4782,77 +4782,17 @@
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="n">
-        <v>46273</v>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C146" s="9" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D146" s="10" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E146" s="10" t="inlineStr">
-        <is>
-          <t>10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="F146" s="10" t="inlineStr">
-        <is>
-          <t>12C1, 12C2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:F146"/>
+  <autoFilter ref="A2:F144"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1949,15 +1949,15 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46262</v>
+        <v>46280</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -1979,20 +1979,20 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2009,20 +2009,20 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46290</v>
+        <v>46338</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
@@ -2039,20 +2039,20 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2223,21 +2223,21 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2249,25 +2249,25 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46266</v>
+        <v>46274</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2313,11 +2313,11 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2339,20 +2339,20 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46296</v>
+        <v>46316</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2429,25 +2429,25 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46316</v>
+        <v>46325</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46325</v>
+        <v>46330</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46330</v>
+        <v>46338</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2519,20 +2519,20 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2579,25 +2579,25 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46266</v>
+        <v>46274</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2613,21 +2613,21 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2639,25 +2639,25 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2673,21 +2673,21 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2699,20 +2699,20 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46296</v>
+        <v>46325</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46325</v>
+        <v>46330</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2759,25 +2759,25 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1002,42 +1002,42 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>46336</v>
+        <v>46265</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -1074,16 +1074,16 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>46321</v>
+        <v>46258</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>46258</v>
+        <v>46293</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -1134,30 +1134,30 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>46293</v>
+        <v>46273</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1173,21 +1173,21 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>46273</v>
+        <v>46303</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1203,11 +1203,11 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46303</v>
+        <v>46330</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1233,28 +1233,28 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>46330</v>
+        <v>46336</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1263,21 +1263,21 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>46336</v>
+        <v>46275</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>46275</v>
+        <v>46336</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -1314,30 +1314,30 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>46336</v>
+        <v>46258</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1353,21 +1353,21 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>46258</v>
+        <v>46273</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1383,11 +1383,11 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>46276</v>
+        <v>46332</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -1443,11 +1443,11 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>46332</v>
+        <v>46335</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1473,37 +1473,37 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46335</v>
+        <v>46350</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>46350</v>
+        <v>46266</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>46266</v>
+        <v>46274</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1563,21 +1563,21 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1589,15 +1589,15 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1623,21 +1623,21 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>46281</v>
+        <v>46296</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1649,25 +1649,25 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>46296</v>
+        <v>46323</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1683,11 +1683,11 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1709,55 +1709,55 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>46325</v>
+        <v>46337</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>46337</v>
+        <v>46261</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>46261</v>
+        <v>46282</v>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>46282</v>
+        <v>46324</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>46324</v>
+        <v>46345</v>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
@@ -1842,42 +1842,42 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Car (Carina Campagnani)</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>46345</v>
+        <v>46260</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>46260</v>
+        <v>46316</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -1914,30 +1914,30 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Car (Carina Campagnani)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46280</v>
+        <v>46325</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -1974,136 +1974,136 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46338</v>
+        <v>46344</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46339</v>
+        <v>46259</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>46286</v>
+        <v>46304</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46344</v>
+        <v>46260</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
@@ -2117,23 +2117,23 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -2154,30 +2154,30 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>46304</v>
+        <v>46274</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2189,25 +2189,25 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>46260</v>
+        <v>46279</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2249,11 +2249,11 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46274</v>
+        <v>46316</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
@@ -2283,11 +2283,11 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46279</v>
+        <v>46322</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2309,20 +2309,20 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46280</v>
+        <v>46325</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
@@ -2339,11 +2339,11 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46283</v>
+        <v>46325</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2369,32 +2369,32 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46296</v>
+        <v>46330</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -2403,28 +2403,28 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46316</v>
+        <v>46266</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -2433,28 +2433,28 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46325</v>
+        <v>46274</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -2463,37 +2463,37 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46330</v>
+        <v>46279</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46338</v>
+        <v>46296</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
@@ -2502,19 +2502,19 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46339</v>
+        <v>46325</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
@@ -2549,20 +2549,20 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46266</v>
+        <v>46325</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46274</v>
+        <v>46330</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
@@ -2604,20 +2604,20 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46279</v>
+        <v>46303</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
@@ -2627,62 +2627,62 @@
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46283</v>
+        <v>46336</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46296</v>
+        <v>46276</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2694,16 +2694,16 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -2724,67 +2724,67 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46330</v>
+        <v>46258</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46339</v>
+        <v>46275</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -2793,28 +2793,28 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46303</v>
+        <v>46286</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -2832,32 +2832,32 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46276</v>
+        <v>46344</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -2867,32 +2867,32 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46325</v>
+        <v>46267</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -2904,20 +2904,20 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46332</v>
+        <v>46316</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -2927,57 +2927,57 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46275</v>
+        <v>46315</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -2987,62 +2987,62 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46286</v>
+        <v>46297</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46336</v>
+        <v>46323</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
@@ -3054,16 +3054,16 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46344</v>
+        <v>46288</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -3084,16 +3084,16 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46267</v>
+        <v>46316</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,28 +3102,28 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
@@ -3132,24 +3132,24 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
@@ -3162,28 +3162,28 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46315</v>
+        <v>46329</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,37 +3192,37 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46297</v>
+        <v>46265</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -3234,76 +3234,76 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46323</v>
+        <v>46321</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46288</v>
+        <v>46265</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46316</v>
+        <v>46274</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,28 +3312,28 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46323</v>
+        <v>46302</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,88 +3342,88 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46259</v>
+        <v>46318</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46329</v>
+        <v>46323</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46265</v>
+        <v>46342</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
@@ -3432,37 +3432,37 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46321</v>
+        <v>46276</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
@@ -3474,7 +3474,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -3483,97 +3483,97 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46265</v>
+        <v>46304</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46302</v>
+        <v>46269</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46318</v>
+        <v>46276</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3582,37 +3582,37 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46323</v>
+        <v>46304</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -3624,16 +3624,16 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46342</v>
+        <v>46314</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
@@ -3642,88 +3642,88 @@
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46304</v>
+        <v>46282</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46268</v>
+        <v>46331</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
@@ -3732,37 +3732,37 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46269</v>
+        <v>46342</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -3774,20 +3774,20 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3797,57 +3797,57 @@
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46304</v>
+        <v>46281</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46314</v>
+        <v>46322</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3857,32 +3857,32 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46268</v>
+        <v>46323</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
@@ -3894,20 +3894,20 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46282</v>
+        <v>46337</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3917,14 +3917,14 @@
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -3933,37 +3933,37 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46331</v>
+        <v>46265</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46342</v>
+        <v>46321</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
@@ -3972,28 +3972,28 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
@@ -4002,19 +4002,19 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -4023,37 +4023,37 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -4074,16 +4074,16 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46323</v>
+        <v>46281</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
@@ -4104,7 +4104,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46337</v>
+        <v>46316</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
@@ -4122,19 +4122,19 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -4143,46 +4143,46 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46338</v>
+        <v>46323</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46265</v>
+        <v>46330</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
@@ -4194,55 +4194,55 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46321</v>
+        <v>46337</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
@@ -4254,25 +4254,25 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46274</v>
+        <v>46317</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
@@ -4284,80 +4284,80 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46274</v>
+        <v>46331</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46281</v>
+        <v>46269</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46316</v>
+        <v>46304</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -4367,23 +4367,23 @@
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46323</v>
+        <v>46267</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -4404,16 +4404,16 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46330</v>
+        <v>46316</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
@@ -4422,32 +4422,32 @@
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46337</v>
+        <v>46266</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4457,342 +4457,102 @@
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46282</v>
+        <v>46315</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46317</v>
+        <v>46273</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>11º e 12º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46331</v>
+        <v>46315</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>Velo (Rodrigo Veloso)</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F137" s="6" t="inlineStr">
-        <is>
-          <t>9C1, 9C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>Velo (Rodrigo Veloso)</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="C138" s="9" t="n">
-        <v>46304</v>
-      </c>
-      <c r="D138" s="10" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="E138" s="10" t="inlineStr">
-        <is>
-          <t>2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F138" s="10" t="inlineStr">
-        <is>
-          <t>9C1, 9C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F139" s="6" t="inlineStr">
-        <is>
-          <t>11C1, 11C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="n">
-        <v>46316</v>
-      </c>
-      <c r="D140" s="10" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="E140" s="10" t="inlineStr">
-        <is>
-          <t>1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F140" s="10" t="inlineStr">
-        <is>
-          <t>11C1, 11C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>10C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E142" s="10" t="inlineStr">
-        <is>
-          <t>4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F142" s="10" t="inlineStr">
-        <is>
-          <t>10C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="n">
-        <v>46273</v>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D144" s="10" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E144" s="10" t="inlineStr">
-        <is>
-          <t>10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="F144" s="10" t="inlineStr">
-        <is>
-          <t>12C1, 12C2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:F144"/>
+  <autoFilter ref="A2:F136"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1014,30 +1014,30 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>46265</v>
+        <v>46343</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º tempo</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -1074,16 +1074,16 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>46258</v>
+        <v>46321</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>46293</v>
+        <v>46258</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -1134,30 +1134,30 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>46273</v>
+        <v>46293</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -1173,21 +1173,21 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>46303</v>
+        <v>46273</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1203,11 +1203,11 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46330</v>
+        <v>46303</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1233,28 +1233,28 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>46336</v>
+        <v>46330</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1263,21 +1263,21 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>46275</v>
+        <v>46336</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>46336</v>
+        <v>46275</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -1314,30 +1314,30 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>46258</v>
+        <v>46336</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1353,21 +1353,21 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>46273</v>
+        <v>46258</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1383,11 +1383,11 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>46332</v>
+        <v>46276</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -1443,11 +1443,11 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1473,37 +1473,37 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46350</v>
+        <v>46335</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>46266</v>
+        <v>46350</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1563,21 +1563,21 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1589,15 +1589,15 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1623,21 +1623,21 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>46296</v>
+        <v>46281</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1649,25 +1649,25 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>46323</v>
+        <v>46296</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1683,11 +1683,11 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1709,55 +1709,55 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>46337</v>
+        <v>46325</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>46261</v>
+        <v>46337</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>46282</v>
+        <v>46261</v>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>46324</v>
+        <v>46282</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>46345</v>
+        <v>46324</v>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
@@ -1842,42 +1842,42 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Car (Carina Campagnani)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>46260</v>
+        <v>46345</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>46316</v>
+        <v>46260</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -1914,30 +1914,30 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Car (Carina Campagnani)</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -1974,30 +1974,30 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46286</v>
+        <v>46325</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2013,11 +2013,11 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46344</v>
+        <v>46286</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -2034,30 +2034,30 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46259</v>
+        <v>46344</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>46304</v>
+        <v>46259</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
@@ -2094,30 +2094,30 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46260</v>
+        <v>46304</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46266</v>
+        <v>46260</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2159,25 +2159,25 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2219,20 +2219,20 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46296</v>
+        <v>46279</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46316</v>
+        <v>46296</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2279,25 +2279,25 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2309,20 +2309,20 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2373,51 +2373,51 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46330</v>
+        <v>46325</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46266</v>
+        <v>46330</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2429,25 +2429,25 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2489,20 +2489,20 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46296</v>
+        <v>46279</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2523,21 +2523,21 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46325</v>
+        <v>46296</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2583,46 +2583,46 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46330</v>
+        <v>46325</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46303</v>
+        <v>46330</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2643,16 +2643,16 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46336</v>
+        <v>46303</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -2664,30 +2664,30 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46276</v>
+        <v>46336</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46332</v>
+        <v>46276</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -2724,60 +2724,60 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46258</v>
+        <v>46332</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -2793,21 +2793,21 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2823,21 +2823,21 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>46336</v>
+        <v>46286</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2853,37 +2853,37 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46344</v>
+        <v>46336</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46267</v>
+        <v>46344</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46316</v>
+        <v>46267</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
@@ -2934,20 +2934,20 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46259</v>
+        <v>46316</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46315</v>
+        <v>46259</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
@@ -2994,30 +2994,30 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46297</v>
+        <v>46336</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3033,37 +3033,37 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46323</v>
+        <v>46297</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46316</v>
+        <v>46288</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
@@ -3132,37 +3132,37 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46259</v>
+        <v>46323</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46329</v>
+        <v>46259</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -3204,25 +3204,25 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46265</v>
+        <v>46329</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3303,21 +3303,21 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3363,21 +3363,21 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46318</v>
+        <v>46302</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3393,21 +3393,21 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3423,11 +3423,11 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46342</v>
+        <v>46323</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46276</v>
+        <v>46342</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46304</v>
+        <v>46276</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
@@ -3504,30 +3504,30 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46268</v>
+        <v>46304</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3543,21 +3543,21 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46304</v>
+        <v>46276</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3633,51 +3633,51 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46314</v>
+        <v>46304</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46268</v>
+        <v>46314</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46282</v>
+        <v>46261</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46331</v>
+        <v>46268</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46342</v>
+        <v>46314</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -3774,25 +3774,25 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46274</v>
+        <v>46331</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
@@ -3809,11 +3809,11 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
@@ -3839,15 +3839,15 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46322</v>
+        <v>46281</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3899,11 +3899,11 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46337</v>
+        <v>46323</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
@@ -3924,30 +3924,30 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46265</v>
+        <v>46337</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
@@ -3984,25 +3984,25 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4019,11 +4019,11 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4079,11 +4079,11 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46316</v>
+        <v>46281</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4139,11 +4139,11 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
@@ -4152,12 +4152,12 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
@@ -4182,12 +4182,12 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4199,11 +4199,11 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46337</v>
+        <v>46330</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
@@ -4212,42 +4212,42 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46282</v>
+        <v>46337</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46317</v>
+        <v>46282</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4302,37 +4302,37 @@
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46269</v>
+        <v>46331</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46304</v>
+        <v>46269</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4374,30 +4374,30 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46267</v>
+        <v>46304</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46316</v>
+        <v>46267</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
@@ -4434,30 +4434,30 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46266</v>
+        <v>46316</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46315</v>
+        <v>46266</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
@@ -4494,16 +4494,16 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46273</v>
+        <v>46315</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -4533,26 +4533,56 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>12C1, 12C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
         <v>46315</v>
       </c>
-      <c r="D136" s="10" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E136" s="10" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
         <is>
           <t>10º e 11º tempos</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F136"/>
+  <autoFilter ref="A2:F137"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>46336</v>
+        <v>46343</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46280</v>
+        <v>46322</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46283</v>
+        <v>46325</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
@@ -2004,175 +2004,175 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46338</v>
+        <v>46286</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46339</v>
+        <v>46344</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>46286</v>
+        <v>46259</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46344</v>
+        <v>46304</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>46304</v>
+        <v>46266</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -2189,11 +2189,11 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
@@ -2219,20 +2219,20 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2249,25 +2249,25 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46274</v>
+        <v>46296</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2279,25 +2279,25 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46279</v>
+        <v>46316</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46280</v>
+        <v>46322</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46283</v>
+        <v>46325</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
@@ -2369,20 +2369,20 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46296</v>
+        <v>46325</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -2399,11 +2399,11 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46316</v>
+        <v>46330</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
@@ -2424,25 +2424,25 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2454,7 +2454,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46330</v>
+        <v>46274</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
@@ -2493,28 +2493,28 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46338</v>
+        <v>46279</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -2523,21 +2523,21 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46339</v>
+        <v>46296</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46266</v>
+        <v>46325</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2583,21 +2583,21 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46274</v>
+        <v>46325</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2613,97 +2613,97 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46279</v>
+        <v>46330</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46283</v>
+        <v>46303</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46296</v>
+        <v>46336</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46325</v>
+        <v>46276</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -2724,67 +2724,67 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46330</v>
+        <v>46332</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46339</v>
+        <v>46258</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46303</v>
+        <v>46275</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
@@ -2807,14 +2807,14 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -2823,46 +2823,46 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>46336</v>
+        <v>46286</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46276</v>
+        <v>46336</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
@@ -2874,50 +2874,50 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46325</v>
+        <v>46344</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46332</v>
+        <v>46267</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -2927,57 +2927,57 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46258</v>
+        <v>46316</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46275</v>
+        <v>46259</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -2987,83 +2987,83 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46286</v>
+        <v>46336</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46336</v>
+        <v>46297</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46344</v>
+        <v>46323</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
@@ -3072,28 +3072,28 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46267</v>
+        <v>46288</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,24 +3102,24 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
@@ -3132,58 +3132,58 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46259</v>
+        <v>46323</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46315</v>
+        <v>46259</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,37 +3192,37 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46297</v>
+        <v>46329</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -3234,85 +3234,85 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46323</v>
+        <v>46265</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46288</v>
+        <v>46321</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46316</v>
+        <v>46265</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -3324,16 +3324,16 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,118 +3342,118 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46259</v>
+        <v>46302</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46329</v>
+        <v>46318</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46265</v>
+        <v>46323</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46321</v>
+        <v>46342</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
@@ -3462,19 +3462,19 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -3483,28 +3483,28 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46265</v>
+        <v>46276</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
@@ -3513,67 +3513,67 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46302</v>
+        <v>46268</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46318</v>
+        <v>46269</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3587,27 +3587,27 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46323</v>
+        <v>46276</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3617,109 +3617,109 @@
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46342</v>
+        <v>46304</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46276</v>
+        <v>46314</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46304</v>
+        <v>46261</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
@@ -3732,37 +3732,37 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46269</v>
+        <v>46314</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -3774,80 +3774,80 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46276</v>
+        <v>46331</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46304</v>
+        <v>46274</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46314</v>
+        <v>46281</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3857,92 +3857,92 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46268</v>
+        <v>46322</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46282</v>
+        <v>46323</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
@@ -3954,16 +3954,16 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46342</v>
+        <v>46265</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
@@ -3972,88 +3972,88 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46274</v>
+        <v>46321</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46280</v>
+        <v>46260</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
@@ -4062,19 +4062,19 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46337</v>
+        <v>46281</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
@@ -4134,85 +4134,85 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46338</v>
+        <v>46316</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46265</v>
+        <v>46323</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46321</v>
+        <v>46330</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46260</v>
+        <v>46337</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
@@ -4242,37 +4242,37 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46274</v>
+        <v>46282</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
@@ -4284,80 +4284,80 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46274</v>
+        <v>46317</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46281</v>
+        <v>46331</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46316</v>
+        <v>46269</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -4367,53 +4367,53 @@
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46323</v>
+        <v>46304</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46330</v>
+        <v>46267</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
@@ -4422,28 +4422,28 @@
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46337</v>
+        <v>46316</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -4464,335 +4464,125 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46282</v>
+        <v>46266</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46331</v>
+        <v>46273</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>11º e 12º tempos</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46269</v>
+        <v>46315</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>Velo (Rodrigo Veloso)</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="C138" s="9" t="n">
-        <v>46304</v>
-      </c>
-      <c r="D138" s="10" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="E138" s="10" t="inlineStr">
-        <is>
-          <t>2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F138" s="10" t="inlineStr">
-        <is>
-          <t>9C1, 9C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F139" s="6" t="inlineStr">
-        <is>
-          <t>11C1, 11C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="n">
-        <v>46316</v>
-      </c>
-      <c r="D140" s="10" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="E140" s="10" t="inlineStr">
-        <is>
-          <t>1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F140" s="10" t="inlineStr">
-        <is>
-          <t>11C1, 11C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>10C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E142" s="10" t="inlineStr">
-        <is>
-          <t>4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F142" s="10" t="inlineStr">
-        <is>
-          <t>10C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="n">
-        <v>46273</v>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D144" s="10" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E144" s="10" t="inlineStr">
-        <is>
-          <t>10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="F144" s="10" t="inlineStr">
-        <is>
-          <t>12C1, 12C2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:F144"/>
+  <autoFilter ref="A2:F137"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -3753,16 +3753,16 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>46329</v>
+        <v>46280</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>46336</v>
+        <v>46329</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>46343</v>
+        <v>46336</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
@@ -1032,42 +1032,42 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>46265</v>
+        <v>46343</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -1104,16 +1104,16 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>46258</v>
+        <v>46321</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>46293</v>
+        <v>46258</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
@@ -1164,30 +1164,30 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>46273</v>
+        <v>46293</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46303</v>
+        <v>46273</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1233,11 +1233,11 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>46330</v>
+        <v>46303</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>46275</v>
+        <v>46344</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1323,16 +1323,16 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>46336</v>
+        <v>46275</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -1344,30 +1344,30 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>46258</v>
+        <v>46336</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>46273</v>
+        <v>46258</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1413,11 +1413,11 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>46332</v>
+        <v>46276</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -1473,11 +1473,11 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1503,37 +1503,37 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>46350</v>
+        <v>46335</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>46266</v>
+        <v>46350</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1559,25 +1559,25 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1593,21 +1593,21 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1619,15 +1619,15 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>46296</v>
+        <v>46281</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1679,25 +1679,25 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>46323</v>
+        <v>46296</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1713,11 +1713,11 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1739,55 +1739,55 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>46337</v>
+        <v>46325</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>46261</v>
+        <v>46337</v>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>46282</v>
+        <v>46261</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>46324</v>
+        <v>46282</v>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
@@ -1842,12 +1842,12 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>46345</v>
+        <v>46324</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
@@ -1872,42 +1872,42 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Car (Carina Campagnani)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>46260</v>
+        <v>46345</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>46316</v>
+        <v>46260</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
@@ -1944,30 +1944,30 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Car (Carina Campagnani)</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1979,20 +1979,20 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2004,30 +2004,30 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46286</v>
+        <v>46339</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46344</v>
+        <v>46286</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2064,30 +2064,30 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>46259</v>
+        <v>46344</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46304</v>
+        <v>46259</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -2124,30 +2124,30 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46260</v>
+        <v>46304</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2163,21 +2163,21 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>46266</v>
+        <v>46260</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2189,25 +2189,25 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2223,21 +2223,21 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46296</v>
+        <v>46279</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46316</v>
+        <v>46296</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2339,20 +2339,20 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -2433,21 +2433,21 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46266</v>
+        <v>46339</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2459,25 +2459,25 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2519,20 +2519,20 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46296</v>
+        <v>46279</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46325</v>
+        <v>46296</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2634,30 +2634,30 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46303</v>
+        <v>46339</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2673,16 +2673,16 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46336</v>
+        <v>46303</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2694,30 +2694,30 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46276</v>
+        <v>46336</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46332</v>
+        <v>46276</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -2754,60 +2754,60 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46258</v>
+        <v>46332</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -2823,21 +2823,21 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46336</v>
+        <v>46286</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2883,37 +2883,37 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46344</v>
+        <v>46336</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46267</v>
+        <v>46344</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46316</v>
+        <v>46267</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
@@ -2964,20 +2964,20 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46259</v>
+        <v>46316</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46336</v>
+        <v>46259</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
@@ -3024,30 +3024,30 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46297</v>
+        <v>46336</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3063,37 +3063,37 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46323</v>
+        <v>46297</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46316</v>
+        <v>46288</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
@@ -3162,37 +3162,37 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46259</v>
+        <v>46323</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46329</v>
+        <v>46259</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -3234,25 +3234,25 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46265</v>
+        <v>46329</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3294,16 +3294,16 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
@@ -3372,12 +3372,12 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3393,21 +3393,21 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46318</v>
+        <v>46302</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3453,11 +3453,11 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46342</v>
+        <v>46323</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
@@ -3467,14 +3467,14 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46276</v>
+        <v>46342</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46304</v>
+        <v>46276</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
@@ -3534,30 +3534,30 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46268</v>
+        <v>46304</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46269</v>
+        <v>46258</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46304</v>
+        <v>46276</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3663,41 +3663,41 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46314</v>
+        <v>46304</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46261</v>
+        <v>46314</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3719,11 +3719,11 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46268</v>
+        <v>46261</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3749,11 +3749,11 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46317</v>
+        <v>46268</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
@@ -3762,12 +3762,12 @@
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
@@ -3792,37 +3792,37 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46274</v>
+        <v>46331</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
@@ -3839,11 +3839,11 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -3869,15 +3869,15 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46322</v>
+        <v>46281</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46337</v>
+        <v>46323</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
@@ -3954,30 +3954,30 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46265</v>
+        <v>46337</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
@@ -4014,25 +4014,25 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -4049,11 +4049,11 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
@@ -4092,12 +4092,12 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4109,11 +4109,11 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46316</v>
+        <v>46281</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
@@ -4152,12 +4152,12 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4169,11 +4169,11 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
@@ -4182,12 +4182,12 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4229,11 +4229,11 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46337</v>
+        <v>46330</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
@@ -4242,42 +4242,42 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46282</v>
+        <v>46337</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46317</v>
+        <v>46282</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -4332,37 +4332,37 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46269</v>
+        <v>46331</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46304</v>
+        <v>46269</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
@@ -4404,30 +4404,30 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46267</v>
+        <v>46304</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46316</v>
+        <v>46267</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
@@ -4464,30 +4464,30 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46266</v>
+        <v>46316</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46315</v>
+        <v>46266</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
@@ -4524,16 +4524,16 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46273</v>
+        <v>46315</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -4563,26 +4563,56 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>12C1, 12C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="n">
         <v>46315</v>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E138" s="10" t="inlineStr">
         <is>
           <t>10º e 11º tempos</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F138" s="10" t="inlineStr">
         <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F137"/>
+  <autoFilter ref="A2:F138"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -2943,16 +2943,16 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46323</v>
+        <v>46335</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>3º e 4º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>46314</v>
+        <v>46331</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -4473,16 +4473,16 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46316</v>
+        <v>46329</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>46304</v>
+        <v>46331</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -873,11 +873,11 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>46343</v>
+        <v>46336</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46336</v>
+        <v>46343</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46314</v>
+        <v>46332</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46304</v>
+        <v>46332</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46297</v>
+        <v>46323</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3093,37 +3093,37 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46323</v>
+        <v>46332</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46288</v>
+        <v>46337</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46316</v>
+        <v>46288</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,37 +3192,37 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46259</v>
+        <v>46323</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46329</v>
+        <v>46259</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -3264,25 +3264,25 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46265</v>
+        <v>46329</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3324,16 +3324,16 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3363,21 +3363,21 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46323</v>
+        <v>46302</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46335</v>
+        <v>46323</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,19 +3492,19 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46276</v>
+        <v>46342</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46304</v>
+        <v>46276</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
@@ -3564,30 +3564,30 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46258</v>
+        <v>46304</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46269</v>
+        <v>46258</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3663,16 +3663,16 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46314</v>
+        <v>46276</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
@@ -3693,46 +3693,46 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46332</v>
+        <v>46314</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46268</v>
+        <v>46332</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46317</v>
+        <v>46268</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3809,11 +3809,11 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3822,37 +3822,37 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46274</v>
+        <v>46331</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -3869,11 +3869,11 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
@@ -3899,15 +3899,15 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46322</v>
+        <v>46281</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3959,11 +3959,11 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46337</v>
+        <v>46323</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
@@ -3984,30 +3984,30 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46265</v>
+        <v>46337</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
@@ -4044,25 +4044,25 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -4079,11 +4079,11 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4139,11 +4139,11 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46316</v>
+        <v>46281</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
@@ -4182,12 +4182,12 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4199,11 +4199,11 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4259,11 +4259,11 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46337</v>
+        <v>46330</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -4272,42 +4272,42 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46282</v>
+        <v>46337</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46317</v>
+        <v>46282</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4362,37 +4362,37 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46269</v>
+        <v>46331</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46332</v>
+        <v>46269</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
@@ -4434,20 +4434,20 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46266</v>
+        <v>46332</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46329</v>
+        <v>46266</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
@@ -4494,16 +4494,16 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46266</v>
+        <v>46329</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46315</v>
+        <v>46266</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
@@ -4554,16 +4554,16 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46273</v>
+        <v>46315</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
@@ -4572,12 +4572,12 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -4593,26 +4593,56 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>12C1, 12C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
         <v>46315</v>
       </c>
-      <c r="D138" s="10" t="inlineStr">
+      <c r="D139" s="6" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E138" s="10" t="inlineStr">
+      <c r="E139" s="6" t="inlineStr">
         <is>
           <t>10º e 11º tempos</t>
         </is>
       </c>
-      <c r="F138" s="10" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F138"/>
+  <autoFilter ref="A2:F139"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46332</v>
+        <v>46323</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>6º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -3123,11 +3123,11 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46337</v>
+        <v>46332</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -3137,23 +3137,23 @@
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46288</v>
+        <v>46337</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46316</v>
+        <v>46288</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
@@ -3222,252 +3222,252 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>11º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46259</v>
+        <v>46316</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46329</v>
+        <v>46316</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46265</v>
+        <v>46323</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46274</v>
+        <v>46329</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46302</v>
+        <v>46265</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46323</v>
+        <v>46321</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46335</v>
+        <v>46265</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
@@ -3513,11 +3513,11 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46342</v>
+        <v>46274</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
@@ -3527,14 +3527,14 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -3543,11 +3543,11 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46276</v>
+        <v>46302</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
@@ -3573,37 +3573,37 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46304</v>
+        <v>46323</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46258</v>
+        <v>46335</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -3612,54 +3612,54 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46269</v>
+        <v>46342</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
@@ -3672,42 +3672,42 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46314</v>
+        <v>46304</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3723,46 +3723,46 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46332</v>
+        <v>46258</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -3774,50 +3774,50 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46268</v>
+        <v>46276</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -3827,92 +3827,92 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46281</v>
+        <v>46268</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
@@ -3924,20 +3924,20 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -3954,25 +3954,25 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46323</v>
+        <v>46331</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
@@ -3989,11 +3989,11 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46337</v>
+        <v>46274</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4014,76 +4014,76 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46260</v>
+        <v>46323</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
@@ -4092,28 +4092,28 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46274</v>
+        <v>46337</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
@@ -4122,72 +4122,72 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46281</v>
+        <v>46321</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46316</v>
+        <v>46260</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46330</v>
+        <v>46274</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46337</v>
+        <v>46281</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4314,25 +4314,25 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46282</v>
+        <v>46316</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
@@ -4344,187 +4344,187 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46317</v>
+        <v>46323</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46269</v>
+        <v>46337</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46332</v>
+        <v>46282</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46266</v>
+        <v>46317</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46329</v>
+        <v>46331</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
@@ -4533,28 +4533,28 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -4563,28 +4563,28 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46315</v>
+        <v>46332</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
@@ -4602,47 +4602,167 @@
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>11C1, 11C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>Ing</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>10C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Ing</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>10C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
           <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>Hist</t>
         </is>
       </c>
-      <c r="C139" s="5" t="n">
+      <c r="C142" s="9" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>12C1, 12C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n">
         <v>46315</v>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D143" s="6" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E143" s="6" t="inlineStr">
         <is>
           <t>10º e 11º tempos</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F139"/>
+  <autoFilter ref="A2:F143"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>46329</v>
+        <v>46336</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1053,21 +1053,21 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>46336</v>
+        <v>46338</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1473,16 +1473,16 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46332</v>
+        <v>46316</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -2763,16 +2763,16 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46332</v>
+        <v>46316</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>4º tempo</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>4º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1713,11 +1713,11 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46322</v>
+        <v>46318</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46323</v>
+        <v>46321</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46335</v>
+        <v>46323</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2784,60 +2784,60 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46258</v>
+        <v>46330</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46336</v>
+        <v>46286</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2913,51 +2913,51 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46344</v>
+        <v>46336</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46273</v>
+        <v>46344</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2973,16 +2973,16 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46316</v>
+        <v>46273</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -2994,20 +2994,20 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46259</v>
+        <v>46316</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46343</v>
+        <v>46259</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
@@ -3054,30 +3054,30 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46323</v>
+        <v>46343</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>6º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3123,21 +3123,21 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46332</v>
+        <v>46323</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>6º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46337</v>
+        <v>46332</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -3167,23 +3167,23 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46288</v>
+        <v>46337</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>11º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>11º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -3342,42 +3342,42 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>4º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46259</v>
+        <v>46330</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º tempo</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46329</v>
+        <v>46259</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -3414,25 +3414,25 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46265</v>
+        <v>46329</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
@@ -3474,16 +3474,16 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46321</v>
+        <v>46302</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46323</v>
+        <v>46321</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3633,11 +3633,11 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46342</v>
+        <v>46323</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
@@ -3647,14 +3647,14 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46276</v>
+        <v>46342</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46304</v>
+        <v>46276</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
@@ -3714,30 +3714,30 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46258</v>
+        <v>46304</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46269</v>
+        <v>46258</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3813,16 +3813,16 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46314</v>
+        <v>46276</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
@@ -3843,46 +3843,46 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46332</v>
+        <v>46314</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46268</v>
+        <v>46332</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46317</v>
+        <v>46268</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3959,11 +3959,11 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
@@ -3972,37 +3972,37 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46274</v>
+        <v>46331</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4019,11 +4019,11 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -4049,15 +4049,15 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46322</v>
+        <v>46281</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4083,21 +4083,21 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -4109,11 +4109,11 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46337</v>
+        <v>46323</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
@@ -4134,30 +4134,30 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46265</v>
+        <v>46337</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
@@ -4194,25 +4194,25 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
@@ -4229,11 +4229,11 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4289,11 +4289,11 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46316</v>
+        <v>46281</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4349,11 +4349,11 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
@@ -4392,12 +4392,12 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4409,11 +4409,11 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46337</v>
+        <v>46330</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
@@ -4422,42 +4422,42 @@
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46282</v>
+        <v>46337</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46317</v>
+        <v>46282</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
@@ -4512,37 +4512,37 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46269</v>
+        <v>46331</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46332</v>
+        <v>46269</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
@@ -4584,20 +4584,20 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46266</v>
+        <v>46332</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46329</v>
+        <v>46266</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
@@ -4644,16 +4644,16 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>46266</v>
+        <v>46329</v>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
@@ -4662,12 +4662,12 @@
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>46315</v>
+        <v>46266</v>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
@@ -4704,16 +4704,16 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>46273</v>
+        <v>46315</v>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
@@ -4722,12 +4722,12 @@
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -4743,26 +4743,56 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>12C1, 12C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
         <v>46315</v>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D144" s="10" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E144" s="10" t="inlineStr">
         <is>
           <t>10º e 11º tempos</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr">
+      <c r="F144" s="10" t="inlineStr">
         <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F143"/>
+  <autoFilter ref="A2:F144"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1473,21 +1473,21 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46316</v>
+        <v>46335</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46316</v>
+        <v>46330</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2793,21 +2793,21 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46330</v>
+        <v>46335</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -4713,11 +4713,11 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>46315</v>
+        <v>46337</v>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46335</v>
+        <v>46321</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46316</v>
+        <v>46302</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46316</v>
+        <v>46302</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3123,21 +3123,21 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>6º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46332</v>
+        <v>46323</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46337</v>
+        <v>46323</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>6º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46316</v>
+        <v>46302</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>46336</v>
+        <v>46317</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1053,21 +1053,21 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>46338</v>
+        <v>46336</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>3º e 4º tempos</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>46304</v>
+        <v>46301</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46304</v>
+        <v>46301</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>46293</v>
+        <v>46314</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -2043,16 +2043,16 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46275</v>
+        <v>46261</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3543,21 +3543,21 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1233,11 +1233,11 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>46303</v>
+        <v>46281</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2673,16 +2673,16 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46303</v>
+        <v>46279</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>46293</v>
+        <v>46314</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1233,11 +1233,11 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>46303</v>
+        <v>46281</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -2043,16 +2043,16 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2673,16 +2673,16 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46303</v>
+        <v>46279</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46275</v>
+        <v>46261</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3543,21 +3543,21 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46269</v>
+        <v>46262</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46269</v>
+        <v>46262</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>46260</v>
+        <v>46302</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
@@ -1944,30 +1944,30 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Car (Carina Campagnani)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46302</v>
+        <v>46322</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1979,20 +1979,20 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46322</v>
+        <v>46339</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2004,30 +2004,30 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46339</v>
+        <v>46275</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2043,16 +2043,16 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46275</v>
+        <v>46344</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2064,30 +2064,30 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>46344</v>
+        <v>46259</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46259</v>
+        <v>46304</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -2124,25 +2124,25 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46304</v>
+        <v>46266</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -2159,11 +2159,11 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
@@ -2189,20 +2189,20 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
@@ -2219,25 +2219,25 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46274</v>
+        <v>46296</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2249,25 +2249,25 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46279</v>
+        <v>46302</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2279,20 +2279,20 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46296</v>
+        <v>46318</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -2309,25 +2309,25 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46302</v>
+        <v>46322</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46318</v>
+        <v>46330</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2369,20 +2369,20 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46322</v>
+        <v>46339</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -2394,60 +2394,60 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46330</v>
+        <v>46266</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46339</v>
+        <v>46274</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2459,20 +2459,20 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -2489,25 +2489,25 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46274</v>
+        <v>46296</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2523,16 +2523,16 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46279</v>
+        <v>46318</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -2549,25 +2549,25 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46296</v>
+        <v>46330</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46318</v>
+        <v>46339</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
@@ -2592,37 +2592,37 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46330</v>
+        <v>46279</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2634,90 +2634,90 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46339</v>
+        <v>46336</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46336</v>
+        <v>46330</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46276</v>
+        <v>46335</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -2754,90 +2754,90 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46330</v>
+        <v>46258</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46335</v>
+        <v>46275</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>46258</v>
+        <v>46275</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2853,11 +2853,11 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46275</v>
+        <v>46336</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2883,37 +2883,37 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46275</v>
+        <v>46344</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46336</v>
+        <v>46273</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
@@ -2927,23 +2927,23 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46344</v>
+        <v>46316</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
@@ -2952,28 +2952,28 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46273</v>
+        <v>46259</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -2994,20 +2994,20 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46316</v>
+        <v>46343</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -3024,60 +3024,60 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46259</v>
+        <v>46316</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46343</v>
+        <v>46318</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3123,37 +3123,37 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>6º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
@@ -3162,28 +3162,28 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>6º tempo</t>
+          <t>11º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>11º tempo</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,97 +3312,97 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>4º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46330</v>
+        <v>46259</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>4º tempo</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -3414,25 +3414,25 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46329</v>
+        <v>46314</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -3444,12 +3444,12 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
@@ -3462,28 +3462,28 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46314</v>
+        <v>46265</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46265</v>
+        <v>46321</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46274</v>
+        <v>46323</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46321</v>
+        <v>46342</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -3612,19 +3612,19 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -3633,28 +3633,28 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46323</v>
+        <v>46276</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -3663,41 +3663,41 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46342</v>
+        <v>46304</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46276</v>
+        <v>46258</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
@@ -3707,23 +3707,23 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46304</v>
+        <v>46262</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46258</v>
+        <v>46269</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3783,16 +3783,16 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46262</v>
+        <v>46314</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46269</v>
+        <v>46332</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3834,20 +3834,20 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46314</v>
+        <v>46268</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3857,37 +3857,37 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46332</v>
+        <v>46268</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46268</v>
+        <v>46317</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46268</v>
+        <v>46331</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
@@ -3954,55 +3954,55 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46317</v>
+        <v>46274</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46331</v>
+        <v>46281</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46274</v>
+        <v>46322</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -4049,11 +4049,11 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46281</v>
+        <v>46323</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -4079,15 +4079,15 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46322</v>
+        <v>46337</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -4097,92 +4097,92 @@
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46323</v>
+        <v>46265</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46337</v>
+        <v>46314</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
@@ -4194,30 +4194,30 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46314</v>
+        <v>46274</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46260</v>
+        <v>46281</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4259,11 +4259,11 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46274</v>
+        <v>46302</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46274</v>
+        <v>46323</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46281</v>
+        <v>46330</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46302</v>
+        <v>46337</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4362,67 +4362,67 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46323</v>
+        <v>46282</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46330</v>
+        <v>46317</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -4434,140 +4434,140 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46337</v>
+        <v>46331</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46282</v>
+        <v>46269</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46317</v>
+        <v>46332</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46331</v>
+        <v>46267</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46269</v>
+        <v>46329</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4577,14 +4577,14 @@
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -4593,37 +4593,37 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46332</v>
+        <v>46266</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46267</v>
+        <v>46337</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
@@ -4632,19 +4632,19 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>46329</v>
+        <v>46273</v>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
@@ -4662,28 +4662,28 @@
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>11º e 12º tempos</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>46266</v>
+        <v>46315</v>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
@@ -4692,107 +4692,17 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="n">
-        <v>46337</v>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="E142" s="10" t="inlineStr">
-        <is>
-          <t>4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F142" s="10" t="inlineStr">
-        <is>
-          <t>10C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="n">
-        <v>46273</v>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D144" s="10" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="E144" s="10" t="inlineStr">
-        <is>
-          <t>10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="F144" s="10" t="inlineStr">
-        <is>
-          <t>12C1, 12C2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:F144"/>
+  <autoFilter ref="A2:F141"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1413,11 +1413,11 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1443,11 +1443,11 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1653,11 +1653,11 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -3993,11 +3993,11 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
@@ -4233,11 +4233,11 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46322</v>
+        <v>46289</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -1979,20 +1979,20 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46339</v>
+        <v>46322</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2004,30 +2004,30 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46275</v>
+        <v>46339</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2043,16 +2043,16 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46344</v>
+        <v>46275</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2064,30 +2064,30 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>46259</v>
+        <v>46344</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46304</v>
+        <v>46259</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -2124,25 +2124,25 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46266</v>
+        <v>46304</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -2159,25 +2159,25 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2219,20 +2219,20 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46296</v>
+        <v>46279</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2249,25 +2249,25 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46302</v>
+        <v>46289</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2279,20 +2279,20 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46318</v>
+        <v>46296</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -2309,25 +2309,25 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46322</v>
+        <v>46302</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46330</v>
+        <v>46318</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2369,20 +2369,20 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46339</v>
+        <v>46322</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -2394,60 +2394,60 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46266</v>
+        <v>46330</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46274</v>
+        <v>46339</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2459,20 +2459,20 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -2489,25 +2489,25 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46296</v>
+        <v>46274</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2523,16 +2523,16 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46318</v>
+        <v>46279</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -2549,25 +2549,25 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46330</v>
+        <v>46296</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46339</v>
+        <v>46318</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
@@ -2592,37 +2592,37 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46279</v>
+        <v>46330</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2634,90 +2634,90 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46336</v>
+        <v>46339</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46330</v>
+        <v>46336</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46335</v>
+        <v>46276</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -2754,90 +2754,90 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46258</v>
+        <v>46330</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46275</v>
+        <v>46335</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -2853,11 +2853,11 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46336</v>
+        <v>46275</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2883,37 +2883,37 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46344</v>
+        <v>46275</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46273</v>
+        <v>46336</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
@@ -2927,23 +2927,23 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46316</v>
+        <v>46344</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
@@ -2952,28 +2952,28 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46259</v>
+        <v>46273</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -2994,20 +2994,20 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46343</v>
+        <v>46316</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -3024,60 +3024,60 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46316</v>
+        <v>46259</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46318</v>
+        <v>46343</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3123,37 +3123,37 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>6º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
@@ -3162,28 +3162,28 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>11º tempo</t>
+          <t>6º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>11º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,97 +3312,97 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>4º tempo</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46259</v>
+        <v>46330</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º tempo</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -3414,25 +3414,25 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46314</v>
+        <v>46329</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -3444,12 +3444,12 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
@@ -3462,28 +3462,28 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46265</v>
+        <v>46314</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46342</v>
+        <v>46321</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -3612,19 +3612,19 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -3633,28 +3633,28 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46276</v>
+        <v>46323</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -3663,41 +3663,41 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46304</v>
+        <v>46342</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
@@ -3707,23 +3707,23 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46262</v>
+        <v>46304</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46269</v>
+        <v>46258</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3783,16 +3783,16 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46314</v>
+        <v>46262</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46332</v>
+        <v>46269</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3834,20 +3834,20 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46268</v>
+        <v>46314</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3857,37 +3857,37 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46268</v>
+        <v>46332</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46317</v>
+        <v>46268</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46331</v>
+        <v>46268</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
@@ -3954,55 +3954,55 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46274</v>
+        <v>46317</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46286</v>
+        <v>46331</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46322</v>
+        <v>46274</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4049,20 +4049,20 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46323</v>
+        <v>46286</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -4079,101 +4079,101 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46337</v>
+        <v>46289</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46265</v>
+        <v>46322</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46314</v>
+        <v>46323</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46274</v>
+        <v>46337</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
@@ -4182,58 +4182,58 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46286</v>
+        <v>46314</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4259,11 +4259,11 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4319,25 +4319,25 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46330</v>
+        <v>46286</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46337</v>
+        <v>46302</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4362,67 +4362,67 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46282</v>
+        <v>46323</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46317</v>
+        <v>46330</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -4434,140 +4434,140 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46332</v>
+        <v>46317</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46267</v>
+        <v>46331</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46329</v>
+        <v>46269</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4577,14 +4577,14 @@
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -4593,37 +4593,37 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46266</v>
+        <v>46332</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46337</v>
+        <v>46267</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
@@ -4632,19 +4632,19 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>46273</v>
+        <v>46329</v>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
@@ -4662,47 +4662,137 @@
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Ing</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>10C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>Ing</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="n">
+        <v>46337</v>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>10C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
           <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>Hist</t>
         </is>
       </c>
-      <c r="C141" s="5" t="n">
+      <c r="C143" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>12C1, 12C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
         <v>46315</v>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D144" s="10" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E144" s="10" t="inlineStr">
         <is>
           <t>10º e 11º tempos</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
+      <c r="F144" s="10" t="inlineStr">
         <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F141"/>
+  <autoFilter ref="A2:F144"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1413,11 +1413,11 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1443,11 +1443,11 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1653,11 +1653,11 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46322</v>
+        <v>46289</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -1979,20 +1979,20 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46339</v>
+        <v>46322</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2004,30 +2004,30 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46275</v>
+        <v>46339</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2043,16 +2043,16 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46344</v>
+        <v>46275</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2064,30 +2064,30 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>46259</v>
+        <v>46344</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46304</v>
+        <v>46259</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -2124,25 +2124,25 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46266</v>
+        <v>46304</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -2159,25 +2159,25 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2219,20 +2219,20 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46296</v>
+        <v>46279</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2249,25 +2249,25 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46302</v>
+        <v>46289</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2279,20 +2279,20 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46318</v>
+        <v>46296</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -2309,25 +2309,25 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46322</v>
+        <v>46302</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46330</v>
+        <v>46318</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2369,20 +2369,20 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46339</v>
+        <v>46322</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -2394,60 +2394,60 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46266</v>
+        <v>46330</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46274</v>
+        <v>46339</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2459,20 +2459,20 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -2489,25 +2489,25 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46296</v>
+        <v>46274</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2523,16 +2523,16 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46318</v>
+        <v>46279</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -2549,25 +2549,25 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46330</v>
+        <v>46296</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46339</v>
+        <v>46318</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
@@ -2592,37 +2592,37 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46279</v>
+        <v>46330</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2634,90 +2634,90 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46336</v>
+        <v>46339</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46330</v>
+        <v>46336</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46335</v>
+        <v>46276</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -2754,90 +2754,90 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46258</v>
+        <v>46330</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46275</v>
+        <v>46335</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -2853,11 +2853,11 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46336</v>
+        <v>46275</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2883,37 +2883,37 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46344</v>
+        <v>46275</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46273</v>
+        <v>46336</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
@@ -2927,23 +2927,23 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46316</v>
+        <v>46344</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
@@ -2952,28 +2952,28 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46259</v>
+        <v>46273</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -2994,20 +2994,20 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46343</v>
+        <v>46316</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -3024,60 +3024,60 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46316</v>
+        <v>46259</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46318</v>
+        <v>46343</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3123,37 +3123,37 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>6º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
@@ -3162,28 +3162,28 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>11º tempo</t>
+          <t>6º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>11º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,97 +3312,97 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>4º tempo</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46259</v>
+        <v>46330</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º tempo</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -3414,25 +3414,25 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46314</v>
+        <v>46329</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -3444,12 +3444,12 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
@@ -3462,28 +3462,28 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46265</v>
+        <v>46314</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46342</v>
+        <v>46321</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -3612,19 +3612,19 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -3633,28 +3633,28 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46276</v>
+        <v>46323</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -3663,41 +3663,41 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46304</v>
+        <v>46342</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
@@ -3707,23 +3707,23 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46262</v>
+        <v>46304</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46269</v>
+        <v>46258</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3783,16 +3783,16 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46314</v>
+        <v>46262</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46332</v>
+        <v>46269</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3834,20 +3834,20 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46268</v>
+        <v>46314</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3857,37 +3857,37 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46268</v>
+        <v>46332</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46317</v>
+        <v>46268</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46331</v>
+        <v>46268</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
@@ -3954,55 +3954,55 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46274</v>
+        <v>46317</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46281</v>
+        <v>46331</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46322</v>
+        <v>46274</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4049,20 +4049,20 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46323</v>
+        <v>46286</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -4079,101 +4079,101 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46337</v>
+        <v>46289</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46265</v>
+        <v>46322</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46314</v>
+        <v>46323</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46274</v>
+        <v>46337</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
@@ -4182,72 +4182,72 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46281</v>
+        <v>46314</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4259,11 +4259,11 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
@@ -4319,25 +4319,25 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46330</v>
+        <v>46286</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46337</v>
+        <v>46302</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4362,67 +4362,67 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46282</v>
+        <v>46323</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46317</v>
+        <v>46330</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -4434,140 +4434,140 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46332</v>
+        <v>46317</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46267</v>
+        <v>46331</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46329</v>
+        <v>46269</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4577,14 +4577,14 @@
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -4593,37 +4593,37 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46266</v>
+        <v>46332</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46337</v>
+        <v>46267</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
@@ -4632,19 +4632,19 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>46273</v>
+        <v>46329</v>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
@@ -4662,47 +4662,137 @@
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Ing</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>10C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>Ing</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="n">
+        <v>46337</v>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>10C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
           <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>Hist</t>
         </is>
       </c>
-      <c r="C141" s="5" t="n">
+      <c r="C143" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>12C1, 12C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
         <v>46315</v>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D144" s="10" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E144" s="10" t="inlineStr">
         <is>
           <t>10º e 11º tempos</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
+      <c r="F144" s="10" t="inlineStr">
         <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F141"/>
+  <autoFilter ref="A2:F144"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -4752,7 +4752,7 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
